--- a/Бюджет шаблон.xlsx
+++ b/Бюджет шаблон.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\Код для бюджета\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="294"/>
+    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="294"/>
   </bookViews>
   <sheets>
     <sheet name="расчет" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$36</definedName>
-    <definedName name="Длина_сделки">расчет!$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">расчет!$A$9:$AG$56</definedName>
+    <definedName name="Длина_сделки">расчет!$K$35</definedName>
   </definedNames>
   <calcPr calcId="162913" fullPrecision="0"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
   <si>
     <t>По номенклатуре:</t>
   </si>
@@ -3103,7 +3103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3549,6 +3549,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5623,11 +5629,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AG44"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="11.45" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="0.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="54.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.6640625" style="1" customWidth="1"/>
@@ -5657,22 +5663,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B1" s="167" t="s">
+      <c r="B1" s="169" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
-      <c r="O1" s="167"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
     </row>
     <row r="2" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="B2" s="2"/>
@@ -5685,11 +5691,11 @@
       <c r="H2" s="5"/>
       <c r="I2" s="2"/>
       <c r="J2" s="6"/>
-      <c r="V2" s="174"/>
-      <c r="W2" s="174"/>
-      <c r="X2" s="174"/>
-      <c r="Y2" s="174"/>
-      <c r="Z2" s="174"/>
+      <c r="V2" s="176"/>
+      <c r="W2" s="176"/>
+      <c r="X2" s="176"/>
+      <c r="Y2" s="176"/>
+      <c r="Z2" s="176"/>
     </row>
     <row r="3" spans="1:30" ht="15" customHeight="1">
       <c r="B3" s="2"/>
@@ -5711,11 +5717,11 @@
       <c r="O3" s="5"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
+      <c r="V3" s="176"/>
+      <c r="W3" s="176"/>
+      <c r="X3" s="176"/>
+      <c r="Y3" s="176"/>
+      <c r="Z3" s="176"/>
     </row>
     <row r="4" spans="1:30" ht="39.75" customHeight="1">
       <c r="B4" s="9"/>
@@ -5733,17 +5739,17 @@
       <c r="M4" s="2"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="176"/>
-      <c r="Q4" s="176"/>
-      <c r="R4" s="176"/>
-      <c r="S4" s="176"/>
-      <c r="T4" s="176"/>
-      <c r="U4" s="176"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
+      <c r="P4" s="178"/>
+      <c r="Q4" s="178"/>
+      <c r="R4" s="178"/>
+      <c r="S4" s="178"/>
+      <c r="T4" s="178"/>
+      <c r="U4" s="178"/>
+      <c r="V4" s="176"/>
+      <c r="W4" s="176"/>
+      <c r="X4" s="176"/>
+      <c r="Y4" s="176"/>
+      <c r="Z4" s="176"/>
     </row>
     <row r="5" spans="1:30" ht="15" customHeight="1">
       <c r="B5" s="12"/>
@@ -5768,18 +5774,18 @@
       <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
-      <c r="V5" s="174"/>
-      <c r="W5" s="174"/>
-      <c r="X5" s="174"/>
-      <c r="Y5" s="174"/>
-      <c r="Z5" s="174"/>
+      <c r="V5" s="176"/>
+      <c r="W5" s="176"/>
+      <c r="X5" s="176"/>
+      <c r="Y5" s="176"/>
+      <c r="Z5" s="176"/>
     </row>
     <row r="6" spans="1:30" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="182" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="182"/>
+      <c r="B6" s="184" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="184"/>
       <c r="D6" s="18"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
@@ -5792,43 +5798,43 @@
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="V6" s="175"/>
-      <c r="W6" s="175"/>
-      <c r="X6" s="175"/>
-      <c r="Y6" s="175"/>
-      <c r="Z6" s="175"/>
+      <c r="V6" s="177"/>
+      <c r="W6" s="177"/>
+      <c r="X6" s="177"/>
+      <c r="Y6" s="177"/>
+      <c r="Z6" s="177"/>
     </row>
     <row r="7" spans="1:30" ht="15" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="185" t="s">
+      <c r="B7" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="168"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="168" t="s">
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="171"/>
+      <c r="K7" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="168"/>
-      <c r="R7" s="168"/>
-      <c r="S7" s="168"/>
-      <c r="T7" s="168"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="168"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="168"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="169"/>
+      <c r="L7" s="170"/>
+      <c r="M7" s="170"/>
+      <c r="N7" s="170"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="170"/>
+      <c r="Q7" s="170"/>
+      <c r="R7" s="170"/>
+      <c r="S7" s="170"/>
+      <c r="T7" s="170"/>
+      <c r="U7" s="170"/>
+      <c r="V7" s="170"/>
+      <c r="W7" s="170"/>
+      <c r="X7" s="170"/>
+      <c r="Y7" s="170"/>
+      <c r="Z7" s="171"/>
     </row>
     <row r="8" spans="1:30" s="22" customFormat="1" ht="54.75" customHeight="1">
       <c r="A8" s="21"/>
@@ -5898,10 +5904,10 @@
       <c r="W8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="X8" s="183" t="s">
+      <c r="X8" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="Y8" s="184"/>
+      <c r="Y8" s="186"/>
       <c r="Z8" s="25" t="s">
         <v>43</v>
       </c>
@@ -5912,10 +5918,10 @@
     </row>
     <row r="9" spans="1:30" s="42" customFormat="1" ht="19.5" customHeight="1">
       <c r="A9" s="31"/>
-      <c r="B9" s="181">
+      <c r="B9" s="183">
         <v>1</v>
       </c>
-      <c r="C9" s="181"/>
+      <c r="C9" s="183"/>
       <c r="D9" s="32"/>
       <c r="E9" s="33"/>
       <c r="F9" s="33">
@@ -6021,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="153" t="e">
-        <f>$U$14/Q11*P10/12*0.3</f>
+        <f>$U$34/Q31*P10/12*0.3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S10" s="59" t="e">
@@ -6029,7 +6035,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T10" s="59" t="e">
-        <f>$U$14/Q11*P10/12*0.7</f>
+        <f>$U$34/Q31*P10/12*0.7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U10" s="59" t="e">
@@ -6060,1054 +6066,2694 @@
       <c r="AC10" s="64"/>
       <c r="AD10" s="65"/>
     </row>
-    <row r="11" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
       <c r="A11" s="43"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="71"/>
+      <c r="B11" s="44">
+        <v>2</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="49"/>
+      <c r="H11" s="50"/>
       <c r="I11" s="50">
-        <f>SUM(I10:I10)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="76"/>
-      <c r="O11" s="50">
-        <f>SUM(O10:O10)</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="78">
-        <f>SUM(Q10:Q10)</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="79"/>
-      <c r="S11" s="50" t="e">
-        <f>SUM(S10:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T11" s="80"/>
-      <c r="U11" s="80" t="e">
-        <f>SUM(U10:U10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V11" s="81"/>
-      <c r="W11" s="82"/>
-      <c r="X11" s="83" t="e">
-        <f>AVERAGE(X10:X10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y11" s="50" t="e">
-        <f>SUM(Y10:Y10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z11" s="84" t="e">
-        <f>(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
+        <f t="shared" ref="I11:I30" si="0">G11*H11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="51">
+        <f t="shared" ref="J11:J30" si="1">I11*14</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="53">
+        <f t="shared" ref="L11:L30" si="2">G11</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="54"/>
+      <c r="N11" s="55" t="e">
+        <f t="shared" ref="N11:N30" si="3">M11/P11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O11" s="56">
+        <f t="shared" ref="O11:O30" si="4">M11*L11</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="58">
+        <f t="shared" ref="Q11:Q30" si="5">P11*L11</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="155" t="e">
+        <f>$U$34/Q31*P11/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S11" s="59" t="e">
+        <f t="shared" ref="S11:S30" si="6">R11*L11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T11" s="59" t="e">
+        <f>$U$34/Q31*P11/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" s="59" t="e">
+        <f t="shared" ref="U11:U30" si="7">T11*L11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V11" s="60" t="e">
+        <f t="shared" ref="V11:V30" si="8">H11/P11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W11" s="55" t="e">
+        <f t="shared" ref="W11:W30" si="9">N11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X11" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y11" s="62" t="e">
+        <f t="shared" ref="Y11:Y30" si="10">L11*(M11+R11)*X11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z11" s="63" t="e">
+        <f t="shared" ref="Z11:Z30" si="11">(I11-O11-S11-U11-Y11-AA11-AC11-AB11)/I11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA11" s="64"/>
       <c r="AB11" s="64"/>
       <c r="AC11" s="64"/>
-      <c r="AD11" s="8"/>
+      <c r="AD11" s="154"/>
     </row>
-    <row r="12" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
       <c r="A12" s="43"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="71" t="s">
+      <c r="B12" s="44">
+        <v>3</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="49"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="54"/>
+      <c r="N12" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O12" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="57"/>
+      <c r="Q12" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="155" t="e">
+        <f>$U$34/Q31*P12/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S12" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T12" s="59" t="e">
+        <f>$U$34/Q31*P12/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V12" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W12" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X12" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y12" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z12" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA12" s="64"/>
+      <c r="AB12" s="64"/>
+      <c r="AC12" s="64"/>
+      <c r="AD12" s="154"/>
+    </row>
+    <row r="13" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A13" s="43"/>
+      <c r="B13" s="44">
+        <v>4</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="49"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="155" t="e">
+        <f>$U$34/Q31*P13/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S13" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T13" s="59" t="e">
+        <f>$U$34/Q31*P13/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W13" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X13" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y13" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z13" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA13" s="64"/>
+      <c r="AB13" s="64"/>
+      <c r="AC13" s="64"/>
+      <c r="AD13" s="154"/>
+    </row>
+    <row r="14" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A14" s="43"/>
+      <c r="B14" s="44">
+        <v>5</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="49"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="54"/>
+      <c r="N14" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O14" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="155" t="e">
+        <f>$U$34/Q31*P14/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S14" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T14" s="153" t="e">
+        <f>$U$34/Q31*P14/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V14" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W14" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X14" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y14" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z14" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA14" s="64"/>
+      <c r="AB14" s="64"/>
+      <c r="AC14" s="64"/>
+      <c r="AD14" s="154"/>
+    </row>
+    <row r="15" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A15" s="43"/>
+      <c r="B15" s="44">
+        <v>6</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="54"/>
+      <c r="N15" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O15" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="155" t="e">
+        <f>$U$34/Q31*P15/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" s="59" t="e">
+        <f>$U$34/Q31*P15/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W15" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X15" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y15" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z15" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA15" s="64"/>
+      <c r="AB15" s="64"/>
+      <c r="AC15" s="64"/>
+      <c r="AD15" s="154"/>
+    </row>
+    <row r="16" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A16" s="43"/>
+      <c r="B16" s="44">
+        <v>7</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="49"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="54"/>
+      <c r="N16" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O16" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="155" t="e">
+        <f>$U$34/Q31*P16/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S16" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T16" s="59" t="e">
+        <f>$U$34/Q31*P16/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W16" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X16" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y16" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z16" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA16" s="64"/>
+      <c r="AB16" s="64"/>
+      <c r="AC16" s="64"/>
+      <c r="AD16" s="154"/>
+    </row>
+    <row r="17" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A17" s="43"/>
+      <c r="B17" s="44">
+        <v>8</v>
+      </c>
+      <c r="C17" s="45"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="49"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L17" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="54"/>
+      <c r="N17" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O17" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="155" t="e">
+        <f>$U$34/Q31*P17/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S17" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T17" s="59" t="e">
+        <f>$U$34/Q31*P17/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W17" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X17" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y17" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z17" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA17" s="64"/>
+      <c r="AB17" s="64"/>
+      <c r="AC17" s="64"/>
+      <c r="AD17" s="154"/>
+    </row>
+    <row r="18" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A18" s="43"/>
+      <c r="B18" s="44">
+        <v>9</v>
+      </c>
+      <c r="C18" s="45"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="49"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="54"/>
+      <c r="N18" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O18" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="155" t="e">
+        <f>$U$34/Q31*P18/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S18" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T18" s="59" t="e">
+        <f>$U$34/Q31*P18/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W18" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X18" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y18" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z18" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA18" s="64"/>
+      <c r="AB18" s="64"/>
+      <c r="AC18" s="64"/>
+      <c r="AD18" s="154"/>
+    </row>
+    <row r="19" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A19" s="43"/>
+      <c r="B19" s="44">
+        <v>10</v>
+      </c>
+      <c r="C19" s="45"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="49"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="54"/>
+      <c r="N19" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O19" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="155" t="e">
+        <f>$U$34/Q31*P19/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S19" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T19" s="59" t="e">
+        <f>$U$34/Q31*P19/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W19" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X19" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y19" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z19" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA19" s="64"/>
+      <c r="AB19" s="64"/>
+      <c r="AC19" s="64"/>
+      <c r="AD19" s="154"/>
+    </row>
+    <row r="20" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A20" s="43"/>
+      <c r="B20" s="44">
+        <v>11</v>
+      </c>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="49"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L20" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="54"/>
+      <c r="N20" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O20" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="155" t="e">
+        <f>$U$34/Q31*P20/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S20" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T20" s="59" t="e">
+        <f>$U$34/Q31*P20/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W20" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X20" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y20" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z20" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA20" s="64"/>
+      <c r="AB20" s="64"/>
+      <c r="AC20" s="64"/>
+      <c r="AD20" s="154"/>
+    </row>
+    <row r="21" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A21" s="43"/>
+      <c r="B21" s="44">
+        <v>12</v>
+      </c>
+      <c r="C21" s="45"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="49"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L21" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="54"/>
+      <c r="N21" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O21" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="155" t="e">
+        <f>$U$34/Q31*P21/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S21" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T21" s="59" t="e">
+        <f>$U$34/Q31*P21/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V21" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W21" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X21" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y21" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z21" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA21" s="64"/>
+      <c r="AB21" s="64"/>
+      <c r="AC21" s="64"/>
+      <c r="AD21" s="154"/>
+    </row>
+    <row r="22" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A22" s="43"/>
+      <c r="B22" s="44">
+        <v>13</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="49"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L22" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="54"/>
+      <c r="N22" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O22" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="155" t="e">
+        <f>$U$34/Q31*P22/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S22" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" s="59" t="e">
+        <f>$U$34/Q31*P22/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V22" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W22" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X22" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y22" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z22" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA22" s="64"/>
+      <c r="AB22" s="64"/>
+      <c r="AC22" s="64"/>
+      <c r="AD22" s="154"/>
+    </row>
+    <row r="23" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A23" s="43"/>
+      <c r="B23" s="44">
+        <v>14</v>
+      </c>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="49"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L23" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="54"/>
+      <c r="N23" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O23" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="155" t="e">
+        <f>$U$34/Q31*P23/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S23" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T23" s="59" t="e">
+        <f>$U$34/Q31*P23/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V23" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W23" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X23" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y23" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z23" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA23" s="64"/>
+      <c r="AB23" s="64"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="154"/>
+    </row>
+    <row r="24" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A24" s="43"/>
+      <c r="B24" s="44">
+        <v>15</v>
+      </c>
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="49"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L24" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="54"/>
+      <c r="N24" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O24" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="155" t="e">
+        <f>$U$34/Q31*P24/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S24" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T24" s="59" t="e">
+        <f>$U$34/Q31*P24/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W24" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X24" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y24" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z24" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA24" s="64"/>
+      <c r="AB24" s="64"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="154"/>
+    </row>
+    <row r="25" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A25" s="43"/>
+      <c r="B25" s="44">
+        <v>16</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="49"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L25" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="54"/>
+      <c r="N25" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="155" t="e">
+        <f>$U$34/Q31*P25/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S25" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" s="59" t="e">
+        <f>$U$34/Q31*P25/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V25" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W25" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X25" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y25" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z25" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA25" s="64"/>
+      <c r="AB25" s="64"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="154"/>
+    </row>
+    <row r="26" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A26" s="43"/>
+      <c r="B26" s="44">
+        <v>17</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="49"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="54"/>
+      <c r="N26" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="155" t="e">
+        <f>$U$34/Q31*P26/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S26" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T26" s="59" t="e">
+        <f>$U$34/Q31*P26/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V26" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W26" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X26" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y26" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z26" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA26" s="64"/>
+      <c r="AB26" s="64"/>
+      <c r="AC26" s="64"/>
+      <c r="AD26" s="154"/>
+    </row>
+    <row r="27" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A27" s="43"/>
+      <c r="B27" s="44">
+        <v>18</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="49"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="54"/>
+      <c r="N27" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="57"/>
+      <c r="Q27" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="153" t="e">
+        <f>$U$34/Q31*P27/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" s="59" t="e">
+        <f>$U$34/Q31*P27/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V27" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W27" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X27" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y27" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z27" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA27" s="64"/>
+      <c r="AB27" s="64"/>
+      <c r="AC27" s="64"/>
+      <c r="AD27" s="154"/>
+    </row>
+    <row r="28" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A28" s="43"/>
+      <c r="B28" s="44">
+        <v>19</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="49"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L28" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="54"/>
+      <c r="N28" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="57"/>
+      <c r="Q28" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="153" t="e">
+        <f>$U$34/Q31*P28/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S28" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T28" s="59" t="e">
+        <f>$U$34/Q31*P28/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V28" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W28" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X28" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y28" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z28" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA28" s="64"/>
+      <c r="AB28" s="64"/>
+      <c r="AC28" s="64"/>
+      <c r="AD28" s="154"/>
+    </row>
+    <row r="29" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A29" s="43"/>
+      <c r="B29" s="44">
+        <v>20</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="49"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L29" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="54"/>
+      <c r="N29" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="155" t="e">
+        <f>$U$34/Q31*P29/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S29" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T29" s="59" t="e">
+        <f>$U$34/Q31*P29/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V29" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W29" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X29" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y29" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z29" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA29" s="64"/>
+      <c r="AB29" s="64"/>
+      <c r="AC29" s="64"/>
+      <c r="AD29" s="154"/>
+    </row>
+    <row r="30" spans="1:30" s="66" customFormat="1" ht="56.25" customHeight="1">
+      <c r="A30" s="43"/>
+      <c r="B30" s="44">
+        <v>21</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="49"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="L30" s="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="54"/>
+      <c r="N30" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O30" s="56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="153" t="e">
+        <f>$U$34/Q31*P30/12*0.3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" s="59" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30" s="59" t="e">
+        <f>$U$34/Q31*P30/12*0.7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" s="59" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V30" s="60" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W30" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X30" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y30" s="62" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z30" s="63" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA30" s="64"/>
+      <c r="AB30" s="64"/>
+      <c r="AC30" s="64"/>
+      <c r="AD30" s="154"/>
+    </row>
+    <row r="31" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="43"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="50">
+        <f>SUM(I10:I30)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="50">
+        <f>SUM(O10:O30)</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="78">
+        <f>SUM(Q10:Q30)</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="79"/>
+      <c r="S31" s="50" t="e">
+        <f>SUM(S10:S30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" s="80"/>
+      <c r="U31" s="80" t="e">
+        <f>SUM(U10:U30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" s="81"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="83" t="e">
+        <f>AVERAGE(X10:X30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y31" s="50" t="e">
+        <f>SUM(Y10:Y30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z31" s="84" t="e">
+        <f>(I31-O31-S31-U31-Y31-AA31-AC31-AB31)/I31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA31" s="64"/>
+      <c r="AB31" s="64"/>
+      <c r="AC31" s="64"/>
+      <c r="AD31" s="8"/>
+    </row>
+    <row r="32" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="43"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="50">
-        <f>I11*1.2</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="89"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="95"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="97"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="82"/>
-      <c r="X12" s="99"/>
-      <c r="Y12" s="100"/>
-      <c r="Z12" s="101"/>
-      <c r="AC12" s="102"/>
-      <c r="AD12" s="65"/>
+      <c r="I32" s="50">
+        <f>I31*1.2</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="89"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="92"/>
+      <c r="P32" s="93"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="95"/>
+      <c r="S32" s="96"/>
+      <c r="T32" s="97"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="81"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="99"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="101"/>
+      <c r="AC32" s="102"/>
+      <c r="AD32" s="65"/>
     </row>
-    <row r="13" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A13" s="103" t="s">
+    <row r="33" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A33" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="177" t="s">
+      <c r="B33" s="179" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="178"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="179"/>
-      <c r="H13" s="179"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="R13" s="106"/>
-      <c r="AD13" s="15"/>
+      <c r="C33" s="180"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="K33" s="105"/>
+      <c r="L33" s="105"/>
+      <c r="R33" s="106"/>
+      <c r="AD33" s="15"/>
     </row>
-    <row r="14" spans="1:30" ht="14.1" customHeight="1">
-      <c r="A14" s="103" t="s">
+    <row r="34" spans="1:30" ht="14.1" customHeight="1">
+      <c r="A34" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="170" t="s">
+      <c r="B34" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
-      <c r="F14" s="171"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="180"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="107"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="109"/>
-      <c r="T14" s="110" t="s">
+      <c r="C34" s="173"/>
+      <c r="D34" s="173"/>
+      <c r="E34" s="173"/>
+      <c r="F34" s="173"/>
+      <c r="G34" s="173"/>
+      <c r="H34" s="173"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="107"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="108"/>
+      <c r="S34" s="109"/>
+      <c r="T34" s="110" t="s">
         <v>82</v>
       </c>
-      <c r="U14" s="111"/>
-      <c r="V14" s="112"/>
-      <c r="W14" s="110"/>
+      <c r="U34" s="111"/>
+      <c r="V34" s="112"/>
+      <c r="W34" s="110"/>
     </row>
-    <row r="15" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A15" s="103" t="s">
+    <row r="35" spans="1:30" s="1" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A35" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="170" t="s">
+      <c r="B35" s="172" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
-      <c r="F15" s="171"/>
-      <c r="G15" s="171"/>
-      <c r="H15" s="171"/>
-      <c r="I15" s="113">
+      <c r="C35" s="173"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="173"/>
+      <c r="G35" s="173"/>
+      <c r="H35" s="173"/>
+      <c r="I35" s="113">
         <v>150</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K15" s="105">
-        <f>I15+I16</f>
+      <c r="K35" s="105">
+        <f>I35+I36</f>
         <v>180</v>
       </c>
-      <c r="L15" s="105"/>
-      <c r="R15" s="108"/>
-      <c r="S15" s="109"/>
-      <c r="U15" s="114"/>
+      <c r="L35" s="105"/>
+      <c r="R35" s="108"/>
+      <c r="S35" s="109"/>
+      <c r="U35" s="114"/>
     </row>
-    <row r="16" spans="1:30" s="42" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A16" s="103" t="s">
+    <row r="36" spans="1:30" s="42" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A36" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="172" t="s">
+      <c r="B36" s="174" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="173"/>
-      <c r="F16" s="173"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="173"/>
-      <c r="I16" s="115">
+      <c r="C36" s="175"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="175"/>
+      <c r="G36" s="175"/>
+      <c r="H36" s="175"/>
+      <c r="I36" s="115">
         <v>30</v>
       </c>
-      <c r="J16" s="116"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="105"/>
-      <c r="N16" s="1" t="s">
+      <c r="J36" s="116"/>
+      <c r="K36" s="105"/>
+      <c r="L36" s="105"/>
+      <c r="N36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="O16" s="117">
-        <f>I11*14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="108"/>
-      <c r="S16" s="109"/>
-      <c r="U16" s="119"/>
+      <c r="O36" s="117">
+        <f>I31*14</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="118"/>
+      <c r="R36" s="108"/>
+      <c r="S36" s="109"/>
+      <c r="U36" s="119"/>
     </row>
-    <row r="17" spans="1:32" ht="14.1" customHeight="1">
-      <c r="A17" s="103" t="s">
+    <row r="37" spans="1:30" ht="14.1" customHeight="1">
+      <c r="A37" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="154" t="s">
+      <c r="B37" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="155"/>
-      <c r="F17" s="155"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="105"/>
-      <c r="L17" s="105"/>
-      <c r="N17" s="1" t="s">
+      <c r="C37" s="157"/>
+      <c r="D37" s="157"/>
+      <c r="E37" s="157"/>
+      <c r="F37" s="157"/>
+      <c r="G37" s="157"/>
+      <c r="H37" s="158"/>
+      <c r="I37" s="120"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="N37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="O17" s="117">
-        <f>I12*14</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="8"/>
-      <c r="U17" s="122"/>
+      <c r="O37" s="117">
+        <f>I32*14</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="8"/>
+      <c r="U37" s="122"/>
     </row>
-    <row r="18" spans="1:32" ht="14.1" customHeight="1">
-      <c r="A18" s="103" t="s">
+    <row r="38" spans="1:30" ht="14.1" customHeight="1">
+      <c r="A38" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="154" t="s">
+      <c r="B38" s="156" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="155"/>
-      <c r="D18" s="155"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="105"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="8"/>
+      <c r="C38" s="157"/>
+      <c r="D38" s="157"/>
+      <c r="E38" s="157"/>
+      <c r="F38" s="157"/>
+      <c r="G38" s="157"/>
+      <c r="H38" s="158"/>
+      <c r="I38" s="123"/>
+      <c r="J38" s="124"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="105"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="8"/>
     </row>
-    <row r="19" spans="1:32" ht="14.1" customHeight="1">
-      <c r="A19" s="103" t="s">
+    <row r="39" spans="1:30" ht="14.1" customHeight="1">
+      <c r="A39" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="154" t="s">
+      <c r="B39" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="156"/>
-      <c r="I19" s="125">
-        <f>I11</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="126"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
+      <c r="C39" s="157"/>
+      <c r="D39" s="157"/>
+      <c r="E39" s="157"/>
+      <c r="F39" s="157"/>
+      <c r="G39" s="157"/>
+      <c r="H39" s="158"/>
+      <c r="I39" s="125">
+        <f>I31</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="126"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="105"/>
+      <c r="M39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
     </row>
-    <row r="20" spans="1:32" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="103" t="s">
+    <row r="40" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1">
+      <c r="A40" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="R20" s="129"/>
-      <c r="U20" s="42"/>
+      <c r="B40" s="127"/>
+      <c r="C40" s="127"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="105"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="R40" s="129"/>
+      <c r="U40" s="42"/>
     </row>
-    <row r="21" spans="1:32" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A21" s="103" t="s">
+    <row r="41" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1">
+      <c r="A41" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="127"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="105"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="R21" s="130"/>
+      <c r="B41" s="127"/>
+      <c r="C41" s="127"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="128"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="R41" s="130"/>
     </row>
-    <row r="22" spans="1:32" s="1" customFormat="1" ht="11.1" customHeight="1">
-      <c r="A22" s="103" t="s">
+    <row r="42" spans="1:30" s="1" customFormat="1" ht="11.1" customHeight="1">
+      <c r="A42" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="128"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="R22" s="129"/>
+      <c r="J42" s="128"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="105"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+      <c r="R42" s="129"/>
     </row>
-    <row r="23" spans="1:32" s="136" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="131" t="s">
+    <row r="43" spans="1:30" s="136" customFormat="1" ht="15" customHeight="1">
+      <c r="A43" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="132" t="s">
+      <c r="B43" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="157" t="s">
+      <c r="C43" s="159" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="158"/>
-      <c r="I23" s="159"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="134"/>
-      <c r="N23" s="134"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="105"/>
-      <c r="Q23" s="135"/>
-      <c r="R23" s="135"/>
+      <c r="D43" s="160"/>
+      <c r="E43" s="160"/>
+      <c r="F43" s="160"/>
+      <c r="G43" s="160"/>
+      <c r="H43" s="160"/>
+      <c r="I43" s="161"/>
+      <c r="J43" s="133"/>
+      <c r="K43" s="134"/>
+      <c r="L43" s="134"/>
+      <c r="M43" s="134"/>
+      <c r="N43" s="134"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="105"/>
+      <c r="Q43" s="135"/>
+      <c r="R43" s="135"/>
     </row>
-    <row r="24" spans="1:32" s="134" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="137"/>
-      <c r="B24" s="67">
+    <row r="44" spans="1:30" s="134" customFormat="1" ht="15" customHeight="1">
+      <c r="A44" s="137"/>
+      <c r="B44" s="67">
         <v>1</v>
       </c>
-      <c r="C24" s="160" t="s">
+      <c r="C44" s="162" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="161"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="161"/>
-      <c r="H24" s="162"/>
-      <c r="I24" s="138">
-        <f>I12</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="139"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="105"/>
-      <c r="Q24" s="135"/>
-      <c r="R24" s="135"/>
-      <c r="S24" s="135"/>
+      <c r="D44" s="163"/>
+      <c r="E44" s="163"/>
+      <c r="F44" s="163"/>
+      <c r="G44" s="163"/>
+      <c r="H44" s="164"/>
+      <c r="I44" s="138">
+        <f>I32</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="139"/>
+      <c r="K44" s="66"/>
+      <c r="L44" s="66"/>
+      <c r="M44" s="66"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="66"/>
+      <c r="P44" s="105"/>
+      <c r="Q44" s="135"/>
+      <c r="R44" s="135"/>
+      <c r="S44" s="135"/>
     </row>
-    <row r="25" spans="1:32" s="66" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="43"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="160" t="s">
+    <row r="45" spans="1:30" s="66" customFormat="1" ht="15" customHeight="1">
+      <c r="A45" s="43"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="161"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="140">
-        <f>I24/120*20</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="139">
-        <f>I25*15</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="141"/>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="135"/>
-      <c r="R25" s="135"/>
-      <c r="S25" s="135"/>
+      <c r="D45" s="163"/>
+      <c r="E45" s="163"/>
+      <c r="F45" s="163"/>
+      <c r="G45" s="163"/>
+      <c r="H45" s="164"/>
+      <c r="I45" s="140">
+        <f>I44/120*20</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="139">
+        <f>I45*15</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="141"/>
+      <c r="P45" s="105"/>
+      <c r="Q45" s="135"/>
+      <c r="R45" s="135"/>
+      <c r="S45" s="135"/>
     </row>
-    <row r="26" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="142"/>
-      <c r="B26" s="67">
+    <row r="46" spans="1:30" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A46" s="142"/>
+      <c r="B46" s="67">
         <v>2</v>
       </c>
-      <c r="C26" s="160" t="s">
+      <c r="C46" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="161"/>
-      <c r="E26" s="161"/>
-      <c r="F26" s="161"/>
-      <c r="G26" s="161"/>
-      <c r="H26" s="162"/>
-      <c r="I26" s="140">
-        <f>I24-I25</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="139"/>
-      <c r="K26" s="136"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="143" t="s">
+      <c r="D46" s="163"/>
+      <c r="E46" s="163"/>
+      <c r="F46" s="163"/>
+      <c r="G46" s="163"/>
+      <c r="H46" s="164"/>
+      <c r="I46" s="140">
+        <f>I44-I45</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="139"/>
+      <c r="K46" s="136"/>
+      <c r="L46" s="136"/>
+      <c r="M46" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="N26" s="144" t="s">
+      <c r="N46" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="P26" s="135"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="135"/>
-      <c r="S26" s="135"/>
-      <c r="T26" s="135"/>
-      <c r="U26" s="135"/>
-      <c r="V26" s="135"/>
-      <c r="W26" s="135"/>
-      <c r="X26" s="135"/>
+      <c r="P46" s="135"/>
+      <c r="Q46" s="135"/>
+      <c r="R46" s="135"/>
+      <c r="S46" s="135"/>
+      <c r="T46" s="135"/>
+      <c r="U46" s="135"/>
+      <c r="V46" s="135"/>
+      <c r="W46" s="135"/>
+      <c r="X46" s="135"/>
     </row>
-    <row r="27" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="142"/>
-      <c r="B27" s="67">
+    <row r="47" spans="1:30" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A47" s="142"/>
+      <c r="B47" s="67">
         <v>3</v>
       </c>
-      <c r="C27" s="160" t="s">
+      <c r="C47" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="161"/>
-      <c r="E27" s="161"/>
-      <c r="F27" s="161"/>
-      <c r="G27" s="161"/>
-      <c r="H27" s="162"/>
-      <c r="I27" s="140" t="e">
-        <f>SUM(I28:I37)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J27" s="139"/>
-      <c r="K27" s="136"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="136"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="135"/>
-      <c r="R27" s="135"/>
-      <c r="S27" s="135"/>
-      <c r="T27" s="135"/>
-      <c r="U27" s="135"/>
-      <c r="V27" s="135"/>
-      <c r="W27" s="135"/>
-      <c r="X27" s="135"/>
+      <c r="D47" s="163"/>
+      <c r="E47" s="163"/>
+      <c r="F47" s="163"/>
+      <c r="G47" s="163"/>
+      <c r="H47" s="164"/>
+      <c r="I47" s="140" t="e">
+        <f>SUM(I48:I57)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J47" s="139"/>
+      <c r="K47" s="136"/>
+      <c r="L47" s="136"/>
+      <c r="M47" s="136"/>
+      <c r="N47" s="136"/>
+      <c r="P47" s="135"/>
+      <c r="Q47" s="135"/>
+      <c r="R47" s="135"/>
+      <c r="S47" s="135"/>
+      <c r="T47" s="135"/>
+      <c r="U47" s="135"/>
+      <c r="V47" s="135"/>
+      <c r="W47" s="135"/>
+      <c r="X47" s="135"/>
     </row>
-    <row r="28" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="142"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="160" t="s">
+    <row r="48" spans="1:30" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A48" s="142"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="161"/>
-      <c r="E28" s="161"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="161"/>
-      <c r="H28" s="162"/>
-      <c r="I28" s="140">
-        <f>O11</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="145"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="143" t="s">
+      <c r="D48" s="163"/>
+      <c r="E48" s="163"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="163"/>
+      <c r="H48" s="164"/>
+      <c r="I48" s="140">
+        <f>O31</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="145"/>
+      <c r="K48" s="136"/>
+      <c r="L48" s="136"/>
+      <c r="M48" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="N28" s="144" t="s">
+      <c r="N48" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="P28" s="135"/>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="135"/>
-      <c r="S28" s="135"/>
-      <c r="T28" s="135"/>
-      <c r="U28" s="135"/>
-      <c r="V28" s="135"/>
-      <c r="W28" s="135"/>
-      <c r="X28" s="135"/>
+      <c r="P48" s="135"/>
+      <c r="Q48" s="135"/>
+      <c r="R48" s="135"/>
+      <c r="S48" s="135"/>
+      <c r="T48" s="135"/>
+      <c r="U48" s="135"/>
+      <c r="V48" s="135"/>
+      <c r="W48" s="135"/>
+      <c r="X48" s="135"/>
     </row>
-    <row r="29" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="142"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="163" t="s">
+    <row r="49" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A49" s="142"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="165" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="164"/>
-      <c r="E29" s="164"/>
-      <c r="F29" s="164"/>
-      <c r="G29" s="164"/>
-      <c r="H29" s="146" t="s">
+      <c r="D49" s="166"/>
+      <c r="E49" s="166"/>
+      <c r="F49" s="166"/>
+      <c r="G49" s="166"/>
+      <c r="H49" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="I29" s="147">
-        <f>IF(H29=D43,I28*3.2%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="145"/>
-      <c r="K29" s="136"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="136"/>
-      <c r="N29" s="136"/>
-      <c r="P29" s="135"/>
-      <c r="Q29" s="135"/>
-      <c r="R29" s="135"/>
-      <c r="S29" s="135"/>
-      <c r="T29" s="135"/>
-      <c r="U29" s="135"/>
-      <c r="V29" s="135"/>
-      <c r="W29" s="135"/>
-      <c r="X29" s="135"/>
+      <c r="I49" s="147">
+        <f>IF(H49=D63,I48*3.2%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="145"/>
+      <c r="K49" s="136"/>
+      <c r="L49" s="136"/>
+      <c r="M49" s="136"/>
+      <c r="N49" s="136"/>
+      <c r="P49" s="135"/>
+      <c r="Q49" s="135"/>
+      <c r="R49" s="135"/>
+      <c r="S49" s="135"/>
+      <c r="T49" s="135"/>
+      <c r="U49" s="135"/>
+      <c r="V49" s="135"/>
+      <c r="W49" s="135"/>
+      <c r="X49" s="135"/>
     </row>
-    <row r="30" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="142"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="160" t="s">
+    <row r="50" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A50" s="142"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="162" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="161"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="161"/>
-      <c r="H30" s="162"/>
-      <c r="I30" s="140" t="e">
-        <f>Y11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J30" s="145"/>
-      <c r="K30" s="136"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="143" t="s">
+      <c r="D50" s="163"/>
+      <c r="E50" s="163"/>
+      <c r="F50" s="163"/>
+      <c r="G50" s="163"/>
+      <c r="H50" s="164"/>
+      <c r="I50" s="140" t="e">
+        <f>Y31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J50" s="145"/>
+      <c r="K50" s="136"/>
+      <c r="L50" s="136"/>
+      <c r="M50" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="N30" s="144" t="s">
+      <c r="N50" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="135"/>
-      <c r="R30" s="135"/>
-      <c r="S30" s="135"/>
-      <c r="T30" s="135"/>
-      <c r="U30" s="135"/>
-      <c r="V30" s="135"/>
-      <c r="W30" s="135"/>
-      <c r="X30" s="135"/>
+      <c r="P50" s="135"/>
+      <c r="Q50" s="135"/>
+      <c r="R50" s="135"/>
+      <c r="S50" s="135"/>
+      <c r="T50" s="135"/>
+      <c r="U50" s="135"/>
+      <c r="V50" s="135"/>
+      <c r="W50" s="135"/>
+      <c r="X50" s="135"/>
     </row>
-    <row r="31" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="142"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="160" t="s">
+    <row r="51" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A51" s="142"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="161"/>
-      <c r="E31" s="161"/>
-      <c r="F31" s="161"/>
-      <c r="G31" s="161"/>
-      <c r="H31" s="162"/>
-      <c r="I31" s="140" t="e">
-        <f>S11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J31" s="145"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="Q31" s="135"/>
-      <c r="R31" s="135"/>
-      <c r="S31" s="135"/>
-      <c r="T31" s="135"/>
-      <c r="U31" s="135"/>
-      <c r="V31" s="135"/>
-      <c r="W31" s="135"/>
-      <c r="X31" s="135"/>
-      <c r="Y31" s="135"/>
-      <c r="Z31" s="135"/>
-      <c r="AA31" s="135"/>
-      <c r="AB31" s="135"/>
-      <c r="AC31" s="135"/>
-      <c r="AD31" s="135"/>
-      <c r="AE31" s="135"/>
-      <c r="AF31" s="135"/>
+      <c r="D51" s="163"/>
+      <c r="E51" s="163"/>
+      <c r="F51" s="163"/>
+      <c r="G51" s="163"/>
+      <c r="H51" s="164"/>
+      <c r="I51" s="140" t="e">
+        <f>S31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J51" s="145"/>
+      <c r="K51" s="136"/>
+      <c r="L51" s="136"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="Q51" s="135"/>
+      <c r="R51" s="135"/>
+      <c r="S51" s="135"/>
+      <c r="T51" s="135"/>
+      <c r="U51" s="135"/>
+      <c r="V51" s="135"/>
+      <c r="W51" s="135"/>
+      <c r="X51" s="135"/>
+      <c r="Y51" s="135"/>
+      <c r="Z51" s="135"/>
+      <c r="AA51" s="135"/>
+      <c r="AB51" s="135"/>
+      <c r="AC51" s="135"/>
+      <c r="AD51" s="135"/>
+      <c r="AE51" s="135"/>
+      <c r="AF51" s="135"/>
     </row>
-    <row r="32" spans="1:32" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="142"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="160" t="s">
+    <row r="52" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A52" s="142"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="162"/>
-      <c r="I32" s="140" t="e">
-        <f>U11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J32" s="145"/>
-      <c r="K32" s="136"/>
-      <c r="L32" s="136"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="Q32" s="135"/>
-      <c r="R32" s="135"/>
-      <c r="S32" s="135"/>
-      <c r="T32" s="135"/>
-      <c r="U32" s="135"/>
-      <c r="V32" s="135"/>
-      <c r="W32" s="135"/>
-      <c r="X32" s="135"/>
-      <c r="Y32" s="135"/>
-      <c r="Z32" s="135"/>
-      <c r="AA32" s="135"/>
-      <c r="AB32" s="135"/>
-      <c r="AC32" s="135"/>
-      <c r="AD32" s="135"/>
-      <c r="AE32" s="135"/>
-      <c r="AF32" s="135"/>
+      <c r="D52" s="163"/>
+      <c r="E52" s="163"/>
+      <c r="F52" s="163"/>
+      <c r="G52" s="163"/>
+      <c r="H52" s="164"/>
+      <c r="I52" s="140" t="e">
+        <f>U31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J52" s="145"/>
+      <c r="K52" s="136"/>
+      <c r="L52" s="136"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="Q52" s="135"/>
+      <c r="R52" s="135"/>
+      <c r="S52" s="135"/>
+      <c r="T52" s="135"/>
+      <c r="U52" s="135"/>
+      <c r="V52" s="135"/>
+      <c r="W52" s="135"/>
+      <c r="X52" s="135"/>
+      <c r="Y52" s="135"/>
+      <c r="Z52" s="135"/>
+      <c r="AA52" s="135"/>
+      <c r="AB52" s="135"/>
+      <c r="AC52" s="135"/>
+      <c r="AD52" s="135"/>
+      <c r="AE52" s="135"/>
+      <c r="AF52" s="135"/>
     </row>
-    <row r="33" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="142"/>
-      <c r="B33" s="163" t="s">
+    <row r="53" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A53" s="142"/>
+      <c r="B53" s="165" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="164"/>
-      <c r="H33" s="146" t="s">
+      <c r="C53" s="166"/>
+      <c r="D53" s="166"/>
+      <c r="E53" s="166"/>
+      <c r="F53" s="166"/>
+      <c r="G53" s="166"/>
+      <c r="H53" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="I33" s="148">
-        <f>IF(H33="ДА",I28*16%/365*Длина_сделки,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="139"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="136"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="Q33" s="135"/>
-      <c r="R33" s="135"/>
-      <c r="S33" s="135"/>
-      <c r="T33" s="135"/>
-      <c r="U33" s="135"/>
-      <c r="V33" s="135"/>
-      <c r="W33" s="135"/>
-      <c r="X33" s="135"/>
-      <c r="Y33" s="135"/>
-      <c r="Z33" s="135"/>
-      <c r="AA33" s="135"/>
-      <c r="AB33" s="135"/>
-      <c r="AC33" s="135"/>
-      <c r="AD33" s="135"/>
-      <c r="AE33" s="135"/>
-      <c r="AF33" s="135"/>
+      <c r="I53" s="148">
+        <f>IF(H53="ДА",I48*16%/365*Длина_сделки,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="139"/>
+      <c r="K53" s="136"/>
+      <c r="L53" s="136"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="Q53" s="135"/>
+      <c r="R53" s="135"/>
+      <c r="S53" s="135"/>
+      <c r="T53" s="135"/>
+      <c r="U53" s="135"/>
+      <c r="V53" s="135"/>
+      <c r="W53" s="135"/>
+      <c r="X53" s="135"/>
+      <c r="Y53" s="135"/>
+      <c r="Z53" s="135"/>
+      <c r="AA53" s="135"/>
+      <c r="AB53" s="135"/>
+      <c r="AC53" s="135"/>
+      <c r="AD53" s="135"/>
+      <c r="AE53" s="135"/>
+      <c r="AF53" s="135"/>
     </row>
-    <row r="34" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A34" s="142"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="165" t="s">
+    <row r="54" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A54" s="142"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="167" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="166"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="161"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="162"/>
-      <c r="I34" s="140">
-        <f>AD11</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="149"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="136"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="R34" s="135"/>
-      <c r="S34" s="135"/>
-      <c r="T34" s="135"/>
-      <c r="U34" s="135"/>
-      <c r="V34" s="135"/>
-      <c r="W34" s="135"/>
-      <c r="X34" s="135"/>
-      <c r="Y34" s="135"/>
-      <c r="Z34" s="135"/>
-      <c r="AA34" s="135"/>
-      <c r="AB34" s="135"/>
-      <c r="AC34" s="135"/>
-      <c r="AD34" s="135"/>
-      <c r="AE34" s="135"/>
-      <c r="AF34" s="135"/>
-      <c r="AG34" s="135"/>
+      <c r="D54" s="168"/>
+      <c r="E54" s="163"/>
+      <c r="F54" s="163"/>
+      <c r="G54" s="163"/>
+      <c r="H54" s="164"/>
+      <c r="I54" s="140">
+        <f>AD31</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="149"/>
+      <c r="K54" s="136"/>
+      <c r="L54" s="136"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="R54" s="135"/>
+      <c r="S54" s="135"/>
+      <c r="T54" s="135"/>
+      <c r="U54" s="135"/>
+      <c r="V54" s="135"/>
+      <c r="W54" s="135"/>
+      <c r="X54" s="135"/>
+      <c r="Y54" s="135"/>
+      <c r="Z54" s="135"/>
+      <c r="AA54" s="135"/>
+      <c r="AB54" s="135"/>
+      <c r="AC54" s="135"/>
+      <c r="AD54" s="135"/>
+      <c r="AE54" s="135"/>
+      <c r="AF54" s="135"/>
+      <c r="AG54" s="135"/>
     </row>
-    <row r="35" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="142"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="160" t="s">
+    <row r="55" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A55" s="142"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="162" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="161"/>
-      <c r="E35" s="161"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="162"/>
-      <c r="I35" s="140">
-        <f>AB11</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="149"/>
-      <c r="K35" s="136"/>
-      <c r="L35" s="136"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="R35" s="135"/>
-      <c r="S35" s="135"/>
-      <c r="T35" s="135"/>
-      <c r="U35" s="135"/>
-      <c r="V35" s="135"/>
-      <c r="W35" s="135"/>
-      <c r="X35" s="135"/>
-      <c r="Y35" s="135"/>
-      <c r="Z35" s="135"/>
-      <c r="AA35" s="135"/>
-      <c r="AB35" s="135"/>
-      <c r="AC35" s="135"/>
-      <c r="AD35" s="135"/>
-      <c r="AE35" s="135"/>
-      <c r="AF35" s="135"/>
-      <c r="AG35" s="135"/>
+      <c r="D55" s="163"/>
+      <c r="E55" s="163"/>
+      <c r="F55" s="163"/>
+      <c r="G55" s="163"/>
+      <c r="H55" s="164"/>
+      <c r="I55" s="140">
+        <f>AB31</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="149"/>
+      <c r="K55" s="136"/>
+      <c r="L55" s="136"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="R55" s="135"/>
+      <c r="S55" s="135"/>
+      <c r="T55" s="135"/>
+      <c r="U55" s="135"/>
+      <c r="V55" s="135"/>
+      <c r="W55" s="135"/>
+      <c r="X55" s="135"/>
+      <c r="Y55" s="135"/>
+      <c r="Z55" s="135"/>
+      <c r="AA55" s="135"/>
+      <c r="AB55" s="135"/>
+      <c r="AC55" s="135"/>
+      <c r="AD55" s="135"/>
+      <c r="AE55" s="135"/>
+      <c r="AF55" s="135"/>
+      <c r="AG55" s="135"/>
     </row>
-    <row r="36" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A36" s="142"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="160" t="s">
+    <row r="56" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A56" s="142"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="161"/>
-      <c r="E36" s="161"/>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="162"/>
-      <c r="I36" s="140">
-        <f>AC11</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="149"/>
-      <c r="K36" s="136"/>
-      <c r="L36" s="136"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="R36" s="135"/>
-      <c r="S36" s="135"/>
-      <c r="T36" s="135"/>
-      <c r="U36" s="135"/>
-      <c r="V36" s="135"/>
-      <c r="W36" s="135"/>
-      <c r="X36" s="135"/>
-      <c r="Y36" s="135"/>
-      <c r="Z36" s="135"/>
-      <c r="AA36" s="135"/>
-      <c r="AB36" s="135"/>
-      <c r="AC36" s="135"/>
-      <c r="AD36" s="135"/>
-      <c r="AE36" s="135"/>
-      <c r="AF36" s="135"/>
-      <c r="AG36" s="135"/>
+      <c r="D56" s="163"/>
+      <c r="E56" s="163"/>
+      <c r="F56" s="163"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="164"/>
+      <c r="I56" s="140">
+        <f>AC31</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="149"/>
+      <c r="K56" s="136"/>
+      <c r="L56" s="136"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="R56" s="135"/>
+      <c r="S56" s="135"/>
+      <c r="T56" s="135"/>
+      <c r="U56" s="135"/>
+      <c r="V56" s="135"/>
+      <c r="W56" s="135"/>
+      <c r="X56" s="135"/>
+      <c r="Y56" s="135"/>
+      <c r="Z56" s="135"/>
+      <c r="AA56" s="135"/>
+      <c r="AB56" s="135"/>
+      <c r="AC56" s="135"/>
+      <c r="AD56" s="135"/>
+      <c r="AE56" s="135"/>
+      <c r="AF56" s="135"/>
+      <c r="AG56" s="135"/>
     </row>
-    <row r="37" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A37" s="142"/>
-      <c r="B37" s="163" t="s">
+    <row r="57" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A57" s="142"/>
+      <c r="B57" s="165" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="164"/>
-      <c r="D37" s="164"/>
-      <c r="E37" s="164"/>
-      <c r="F37" s="164"/>
-      <c r="G37" s="164"/>
-      <c r="H37" s="146" t="s">
+      <c r="C57" s="166"/>
+      <c r="D57" s="166"/>
+      <c r="E57" s="166"/>
+      <c r="F57" s="166"/>
+      <c r="G57" s="166"/>
+      <c r="H57" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="I37" s="147">
-        <f>IF(H37="ДА",I24*3%/365*(I15+I16),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="139"/>
-      <c r="K37" s="136"/>
-      <c r="L37" s="136"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="R37" s="135"/>
-      <c r="S37" s="135"/>
-      <c r="T37" s="135"/>
-      <c r="U37" s="135"/>
-      <c r="V37" s="135"/>
-      <c r="W37" s="135"/>
-      <c r="X37" s="135"/>
-      <c r="Y37" s="135"/>
-      <c r="Z37" s="135"/>
-      <c r="AA37" s="135"/>
-      <c r="AB37" s="135"/>
-      <c r="AC37" s="135"/>
-      <c r="AD37" s="135"/>
-      <c r="AE37" s="135"/>
-      <c r="AF37" s="135"/>
-      <c r="AG37" s="135"/>
+      <c r="I57" s="147">
+        <f>IF(H57="ДА",I44*3%/365*(I35+I36),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="139"/>
+      <c r="K57" s="136"/>
+      <c r="L57" s="136"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="R57" s="135"/>
+      <c r="S57" s="135"/>
+      <c r="T57" s="135"/>
+      <c r="U57" s="135"/>
+      <c r="V57" s="135"/>
+      <c r="W57" s="135"/>
+      <c r="X57" s="135"/>
+      <c r="Y57" s="135"/>
+      <c r="Z57" s="135"/>
+      <c r="AA57" s="135"/>
+      <c r="AB57" s="135"/>
+      <c r="AC57" s="135"/>
+      <c r="AD57" s="135"/>
+      <c r="AE57" s="135"/>
+      <c r="AF57" s="135"/>
+      <c r="AG57" s="135"/>
     </row>
-    <row r="38" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A38" s="142"/>
-      <c r="B38" s="67">
+    <row r="58" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A58" s="142"/>
+      <c r="B58" s="67">
         <v>4</v>
       </c>
-      <c r="C38" s="160" t="s">
+      <c r="C58" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="140" t="e">
-        <f>I26-I27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J38" s="139" t="e">
-        <f>I38*15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K38" s="150"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="R38" s="135"/>
-      <c r="S38" s="135"/>
-      <c r="T38" s="135"/>
-      <c r="U38" s="135"/>
-      <c r="V38" s="135"/>
-      <c r="W38" s="135"/>
-      <c r="X38" s="135"/>
-      <c r="Y38" s="135"/>
-      <c r="Z38" s="135"/>
-      <c r="AA38" s="135"/>
-      <c r="AB38" s="135"/>
-      <c r="AC38" s="135"/>
-      <c r="AD38" s="135"/>
-      <c r="AE38" s="135"/>
-      <c r="AF38" s="135"/>
-      <c r="AG38" s="135"/>
+      <c r="D58" s="163"/>
+      <c r="E58" s="163"/>
+      <c r="F58" s="163"/>
+      <c r="G58" s="163"/>
+      <c r="H58" s="164"/>
+      <c r="I58" s="140" t="e">
+        <f>I46-I47</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J58" s="139" t="e">
+        <f>I58*15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K58" s="150"/>
+      <c r="L58" s="136"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="R58" s="135"/>
+      <c r="S58" s="135"/>
+      <c r="T58" s="135"/>
+      <c r="U58" s="135"/>
+      <c r="V58" s="135"/>
+      <c r="W58" s="135"/>
+      <c r="X58" s="135"/>
+      <c r="Y58" s="135"/>
+      <c r="Z58" s="135"/>
+      <c r="AA58" s="135"/>
+      <c r="AB58" s="135"/>
+      <c r="AC58" s="135"/>
+      <c r="AD58" s="135"/>
+      <c r="AE58" s="135"/>
+      <c r="AF58" s="135"/>
+      <c r="AG58" s="135"/>
     </row>
-    <row r="39" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A39" s="142"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="160" t="s">
+    <row r="59" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A59" s="142"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="161"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="140"/>
-      <c r="J39" s="149"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="136"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="R39" s="135"/>
-      <c r="S39" s="135"/>
-      <c r="T39" s="135"/>
-      <c r="U39" s="135"/>
-      <c r="V39" s="135"/>
-      <c r="W39" s="135"/>
-      <c r="X39" s="135"/>
-      <c r="Y39" s="135"/>
-      <c r="Z39" s="135"/>
-      <c r="AA39" s="135"/>
-      <c r="AB39" s="135"/>
-      <c r="AC39" s="135"/>
-      <c r="AD39" s="135"/>
-      <c r="AE39" s="135"/>
-      <c r="AF39" s="135"/>
-      <c r="AG39" s="135"/>
+      <c r="D59" s="163"/>
+      <c r="E59" s="163"/>
+      <c r="F59" s="163"/>
+      <c r="G59" s="163"/>
+      <c r="H59" s="164"/>
+      <c r="I59" s="140"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="136"/>
+      <c r="L59" s="136"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="R59" s="135"/>
+      <c r="S59" s="135"/>
+      <c r="T59" s="135"/>
+      <c r="U59" s="135"/>
+      <c r="V59" s="135"/>
+      <c r="W59" s="135"/>
+      <c r="X59" s="135"/>
+      <c r="Y59" s="135"/>
+      <c r="Z59" s="135"/>
+      <c r="AA59" s="135"/>
+      <c r="AB59" s="135"/>
+      <c r="AC59" s="135"/>
+      <c r="AD59" s="135"/>
+      <c r="AE59" s="135"/>
+      <c r="AF59" s="135"/>
+      <c r="AG59" s="135"/>
     </row>
-    <row r="40" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="142"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="160" t="s">
+    <row r="60" spans="1:33" s="105" customFormat="1" ht="15" customHeight="1">
+      <c r="A60" s="142"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="161"/>
-      <c r="E40" s="161"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="161"/>
-      <c r="H40" s="162"/>
-      <c r="I40" s="151" t="e">
-        <f>I38/I26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J40" s="152"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="136"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="R40" s="135"/>
-      <c r="S40" s="135"/>
-      <c r="T40" s="135"/>
-      <c r="U40" s="135"/>
-      <c r="V40" s="135"/>
-      <c r="W40" s="135"/>
-      <c r="X40" s="135"/>
-      <c r="Y40" s="135"/>
-      <c r="Z40" s="135"/>
-      <c r="AA40" s="135"/>
-      <c r="AB40" s="135"/>
-      <c r="AC40" s="135"/>
-      <c r="AD40" s="135"/>
-      <c r="AE40" s="135"/>
-      <c r="AF40" s="135"/>
-      <c r="AG40" s="135"/>
+      <c r="D60" s="163"/>
+      <c r="E60" s="163"/>
+      <c r="F60" s="163"/>
+      <c r="G60" s="163"/>
+      <c r="H60" s="164"/>
+      <c r="I60" s="151" t="e">
+        <f>I58/I46</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J60" s="152"/>
+      <c r="K60" s="136"/>
+      <c r="L60" s="136"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="R60" s="135"/>
+      <c r="S60" s="135"/>
+      <c r="T60" s="135"/>
+      <c r="U60" s="135"/>
+      <c r="V60" s="135"/>
+      <c r="W60" s="135"/>
+      <c r="X60" s="135"/>
+      <c r="Y60" s="135"/>
+      <c r="Z60" s="135"/>
+      <c r="AA60" s="135"/>
+      <c r="AB60" s="135"/>
+      <c r="AC60" s="135"/>
+      <c r="AD60" s="135"/>
+      <c r="AE60" s="135"/>
+      <c r="AF60" s="135"/>
+      <c r="AG60" s="135"/>
     </row>
-    <row r="41" spans="1:33" s="105" customFormat="1" ht="12" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="R41" s="8"/>
-      <c r="S41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="8"/>
-      <c r="X41" s="8"/>
-      <c r="Y41" s="8"/>
-      <c r="Z41" s="8"/>
-      <c r="AA41" s="8"/>
-      <c r="AB41" s="8"/>
-      <c r="AC41" s="8"/>
-      <c r="AD41" s="8"/>
-      <c r="AE41" s="8"/>
-      <c r="AF41" s="8"/>
-      <c r="AG41" s="8"/>
+    <row r="61" spans="1:33" s="105" customFormat="1" ht="12" customHeight="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="128"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="R61" s="8"/>
+      <c r="S61" s="8"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="8"/>
+      <c r="V61" s="8"/>
+      <c r="W61" s="8"/>
+      <c r="X61" s="8"/>
+      <c r="Y61" s="8"/>
+      <c r="Z61" s="8"/>
+      <c r="AA61" s="8"/>
+      <c r="AB61" s="8"/>
+      <c r="AC61" s="8"/>
+      <c r="AD61" s="8"/>
+      <c r="AE61" s="8"/>
+      <c r="AF61" s="8"/>
+      <c r="AG61" s="8"/>
     </row>
-    <row r="42" spans="1:33" s="1" customFormat="1" ht="11.25" customHeight="1">
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="J42" s="128"/>
-      <c r="P42" s="105"/>
-      <c r="Q42" s="105"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="8"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="8"/>
-      <c r="AF42" s="8"/>
-      <c r="AG42" s="8"/>
+    <row r="62" spans="1:33" s="1" customFormat="1" ht="11.25" customHeight="1">
+      <c r="C62" s="42"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="J62" s="128"/>
+      <c r="P62" s="105"/>
+      <c r="Q62" s="105"/>
+      <c r="R62" s="8"/>
+      <c r="S62" s="8"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="8"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="8"/>
+      <c r="X62" s="8"/>
+      <c r="Y62" s="8"/>
+      <c r="Z62" s="8"/>
+      <c r="AA62" s="8"/>
+      <c r="AB62" s="8"/>
+      <c r="AC62" s="8"/>
+      <c r="AD62" s="8"/>
+      <c r="AE62" s="8"/>
+      <c r="AF62" s="8"/>
+      <c r="AG62" s="8"/>
     </row>
-    <row r="43" spans="1:33" s="1" customFormat="1" ht="11.45" customHeight="1">
-      <c r="C43" s="1" t="s">
+    <row r="63" spans="1:33" s="1" customFormat="1" ht="11.45" customHeight="1">
+      <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J43" s="128"/>
-      <c r="P43" s="105"/>
-      <c r="Q43" s="105"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="8"/>
-      <c r="W43" s="8"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="8"/>
-      <c r="Z43" s="8"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="8"/>
-      <c r="AF43" s="8"/>
-      <c r="AG43" s="8"/>
+      <c r="J63" s="128"/>
+      <c r="P63" s="105"/>
+      <c r="Q63" s="105"/>
+      <c r="R63" s="8"/>
+      <c r="S63" s="8"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="8"/>
+      <c r="V63" s="8"/>
+      <c r="W63" s="8"/>
+      <c r="X63" s="8"/>
+      <c r="Y63" s="8"/>
+      <c r="Z63" s="8"/>
+      <c r="AA63" s="8"/>
+      <c r="AB63" s="8"/>
+      <c r="AC63" s="8"/>
+      <c r="AD63" s="8"/>
+      <c r="AE63" s="8"/>
+      <c r="AF63" s="8"/>
+      <c r="AG63" s="8"/>
     </row>
-    <row r="44" spans="1:33" ht="11.45" customHeight="1">
-      <c r="C44" s="1" t="s">
+    <row r="64" spans="1:33" ht="11.45" customHeight="1">
+      <c r="C64" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J44" s="128"/>
+      <c r="J64" s="128"/>
     </row>
   </sheetData>
   <sortState ref="B9:AC15">
@@ -7116,50 +8762,50 @@
   <mergeCells count="34">
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="K7:Z7"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:H36"/>
     <mergeCell ref="V2:Z6"/>
     <mergeCell ref="P4:U4"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="X8:Y8"/>
     <mergeCell ref="B7:J7"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="C54:H54"/>
+    <mergeCell ref="C55:H55"/>
+    <mergeCell ref="C56:H56"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="C59:H59"/>
+    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="C43:I43"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C45:H45"/>
   </mergeCells>
-  <conditionalFormatting sqref="I40">
+  <conditionalFormatting sqref="I60">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33 H37">
-      <formula1>$C$43:$C$44</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53 H57">
+      <formula1>$C$63:$C$64</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H29">
-      <formula1>$D$43:$D$44</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49">
+      <formula1>$D$63:$D$64</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.15748031496062992" right="0.19685039370078741" top="0.15748031496062992" bottom="0.15748031496062992" header="0.23622047244094491" footer="0.15748031496062992"/>
